--- a/artfynd/A 1881-2021 artfynd.xlsx
+++ b/artfynd/A 1881-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1881-2021 artfynd.xlsx
+++ b/artfynd/A 1881-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104159547</v>
+        <v>104159543</v>
       </c>
       <c r="B7" t="n">
-        <v>89403</v>
+        <v>89412</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1252,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>619763.8936870663</v>
+        <v>619707.4851620743</v>
       </c>
       <c r="R7" t="n">
-        <v>7110983.543032441</v>
+        <v>7110855.776386199</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104159543</v>
+        <v>104159544</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
+        <v>89403</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>619707.4851620743</v>
+        <v>619775.8591510046</v>
       </c>
       <c r="R8" t="n">
-        <v>7110855.776386199</v>
+        <v>7110968.68972041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104159544</v>
+        <v>104159539</v>
       </c>
       <c r="B9" t="n">
-        <v>89403</v>
+        <v>78569</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>619775.8591510046</v>
+        <v>619926.0567874461</v>
       </c>
       <c r="R9" t="n">
-        <v>7110968.68972041</v>
+        <v>7110959.616538647</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104159539</v>
+        <v>104159542</v>
       </c>
       <c r="B10" t="n">
         <v>78569</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>619926.0567874461</v>
+        <v>619761.1012833294</v>
       </c>
       <c r="R10" t="n">
-        <v>7110959.616538647</v>
+        <v>7110817.586914655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104159542</v>
+        <v>104159537</v>
       </c>
       <c r="B11" t="n">
         <v>78569</v>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>619761.1012833294</v>
+        <v>619934.2171344531</v>
       </c>
       <c r="R11" t="n">
-        <v>7110817.586914655</v>
+        <v>7110963.870414373</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104159537</v>
+        <v>104159541</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>619934.2171344531</v>
+        <v>619760.8999961435</v>
       </c>
       <c r="R12" t="n">
-        <v>7110963.870414373</v>
+        <v>7110811.45265131</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104159541</v>
+        <v>112606264</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
+        <v>89782</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,25 +1954,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>619760.8999961435</v>
+        <v>619764</v>
       </c>
       <c r="R13" t="n">
-        <v>7110811.45265131</v>
+        <v>7110984</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,24 +2015,14 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,862 +2046,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112606257</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>619934</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7110964</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112606261</v>
-      </c>
-      <c r="B15" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>619761</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7110818</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112606260</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78920</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>619761</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7110811</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112606262</v>
-      </c>
-      <c r="B17" t="n">
-        <v>89791</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>619707</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7110856</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>112606264</v>
-      </c>
-      <c r="B18" t="n">
-        <v>89782</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1205</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Stor aspticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Phellinus populicola</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>619764</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7110984</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>112606259</v>
-      </c>
-      <c r="B19" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>619796</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7110855</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>112606263</v>
-      </c>
-      <c r="B20" t="n">
-        <v>89782</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1205</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Stor aspticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Phellinus populicola</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>619776</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7110969</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>112606258</v>
-      </c>
-      <c r="B21" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Östernoret, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>619926</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7110960</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
